--- a/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 19,51</t>
+          <t>-1,16; 19,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 13,48</t>
+          <t>-7,02; 13,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 9,78</t>
+          <t>-15,29; 10,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 9,01</t>
+          <t>-5,13; 7,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 180,26</t>
+          <t>-7,85; 200,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 117,06</t>
+          <t>-34,93; 117,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 47,23</t>
+          <t>-46,66; 50,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,77</t>
+          <t>-5,66; 9,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 3,18</t>
+          <t>-22,21; 2,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 11,03</t>
+          <t>-16,27; 9,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 7,96</t>
+          <t>-14,19; 9,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 7,44</t>
+          <t>-7,65; 6,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 12,86</t>
+          <t>-52,29; 9,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 49,11</t>
+          <t>-43,22; 42,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 28,84</t>
+          <t>-34,41; 32,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 8,58</t>
+          <t>-8,16; 7,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,67; -2,06</t>
+          <t>-23,73; -3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 13,91</t>
+          <t>-9,61; 12,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 12,27</t>
+          <t>-11,82; 11,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 11,16</t>
+          <t>-18,79; 10,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,93; -6,41</t>
+          <t>-77,33; -12,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 97,44</t>
+          <t>-40,13; 90,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 126,26</t>
+          <t>-51,99; 104,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 16,15</t>
+          <t>-22,5; 14,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 12,9</t>
+          <t>-3,87; 13,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 13,83</t>
+          <t>-4,03; 14,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 12,02</t>
+          <t>-4,19; 12,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 2,6</t>
+          <t>-14,31; 2,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 51,86</t>
+          <t>-11,12; 56,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 54,8</t>
+          <t>-11,49; 58,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 47,41</t>
+          <t>-12,7; 52,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 3,04</t>
+          <t>-15,93; 3,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 10,8</t>
+          <t>-16,18; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 0,78</t>
+          <t>-24,26; -0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 4,99</t>
+          <t>-17,61; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 12,07</t>
+          <t>-2,64; 12,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 23,13</t>
+          <t>-28,52; 21,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 1,67</t>
+          <t>-41,73; -0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 13,4</t>
+          <t>-35,6; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 14,94</t>
+          <t>-3,0; 15,82</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 14,77</t>
+          <t>-10,44; 15,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 27,1</t>
+          <t>-0,97; 28,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 13,87</t>
+          <t>-18,15; 11,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 10,1</t>
+          <t>-10,55; 10,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 25,48</t>
+          <t>-15,09; 28,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 61,51</t>
+          <t>-3,21; 64,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 37,02</t>
+          <t>-33,22; 30,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 12,62</t>
+          <t>-11,59; 13,93</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,64</t>
+          <t>-4,99; 4,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 6,25</t>
+          <t>-4,09; 5,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,24</t>
+          <t>-5,0; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,12</t>
+          <t>-4,66; 3,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 14,12</t>
+          <t>-13,41; 14,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 19,97</t>
+          <t>-11,38; 17,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 13,96</t>
+          <t>-14,12; 15,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,65</t>
+          <t>-5,31; 3,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 19,79</t>
+          <t>-1,25; 20,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 13,21</t>
+          <t>-7,87; 13,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 10,65</t>
+          <t>-14,64; 9,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,95</t>
+          <t>-4,95; 8,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 200,05</t>
+          <t>-11,36; 203,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 117,68</t>
+          <t>-37,23; 111,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 50,48</t>
+          <t>-44,56; 49,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 9,42</t>
+          <t>-5,33; 10,18</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 2,48</t>
+          <t>-22,33; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 9,52</t>
+          <t>-16,07; 10,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 9,7</t>
+          <t>-14,15; 8,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 6,33</t>
+          <t>-7,41; 6,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 9,97</t>
+          <t>-53,58; 5,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 42,1</t>
+          <t>-44,16; 43,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 32,54</t>
+          <t>-35,32; 27,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 7,32</t>
+          <t>-7,98; 7,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -3,48</t>
+          <t>-22,14; -2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 12,65</t>
+          <t>-8,18; 14,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 11,86</t>
+          <t>-11,86; 11,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 10,03</t>
+          <t>-17,58; 11,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,33; -12,05</t>
+          <t>-77,2; -9,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 90,17</t>
+          <t>-32,04; 108,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 104,41</t>
+          <t>-54,09; 109,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 14,46</t>
+          <t>-21,53; 16,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 13,59</t>
+          <t>-4,0; 12,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 14,3</t>
+          <t>-4,21; 14,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 12,93</t>
+          <t>-4,37; 11,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 2,92</t>
+          <t>-13,33; 3,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 56,15</t>
+          <t>-11,9; 51,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 58,63</t>
+          <t>-13,21; 57,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 52,69</t>
+          <t>-12,66; 46,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 3,4</t>
+          <t>-15,15; 3,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 9,69</t>
+          <t>-15,52; 10,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -0,79</t>
+          <t>-24,14; -0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 4,59</t>
+          <t>-18,35; 5,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 12,48</t>
+          <t>-1,73; 12,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 21,42</t>
+          <t>-26,57; 22,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -0,34</t>
+          <t>-41,56; -0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 12,07</t>
+          <t>-36,97; 14,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 15,82</t>
+          <t>-2,01; 15,67</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 15,43</t>
+          <t>-11,1; 15,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 28,46</t>
+          <t>-1,55; 28,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 11,64</t>
+          <t>-16,14; 12,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 10,86</t>
+          <t>-9,88; 10,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 28,5</t>
+          <t>-15,53; 26,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 64,63</t>
+          <t>-1,37; 70,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 30,31</t>
+          <t>-31,85; 34,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 13,93</t>
+          <t>-11,12; 12,98</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 4,73</t>
+          <t>-4,85; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,5</t>
+          <t>-3,61; 5,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,62</t>
+          <t>-5,84; 3,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,04</t>
+          <t>-4,76; 2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 14,11</t>
+          <t>-12,85; 13,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 17,67</t>
+          <t>-10,05; 18,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 15,02</t>
+          <t>-16,39; 12,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 3,56</t>
+          <t>-5,39; 3,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 20,03</t>
+          <t>-1,56; 19,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 13,2</t>
+          <t>-7,86; 13,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 9,77</t>
+          <t>-13,99; 9,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 8,47</t>
+          <t>-4,13; 10,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 203,05</t>
+          <t>-9,84; 180,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 111,2</t>
+          <t>-40,5; 117,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 49,2</t>
+          <t>-43,79; 47,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 10,18</t>
+          <t>-4,51; 12,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,14%</t>
+          <t>-0,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 2,26</t>
+          <t>-22,37; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 10,46</t>
+          <t>-15,17; 11,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 8,36</t>
+          <t>-14,69; 7,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,23</t>
+          <t>-7,95; 7,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 5,77</t>
+          <t>-52,13; 12,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 43,14</t>
+          <t>-40,27; 49,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 27,39</t>
+          <t>-36,83; 28,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 7,25</t>
+          <t>-8,6; 8,66</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,53</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,57%</t>
+          <t>-8,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -2,43</t>
+          <t>-21,67; -2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 14,05</t>
+          <t>-9,53; 13,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 11,73</t>
+          <t>-10,06; 12,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 11,32</t>
+          <t>-22,69; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,2; -9,77</t>
+          <t>-75,93; -6,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 108,79</t>
+          <t>-36,62; 97,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 109,0</t>
+          <t>-48,79; 126,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 16,14</t>
+          <t>-26,7; 9,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,67%</t>
+          <t>-1,59%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 12,96</t>
+          <t>-4,65; 12,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 14,39</t>
+          <t>-3,78; 13,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 11,83</t>
+          <t>-4,83; 12,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 3,17</t>
+          <t>-7,52; 4,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 51,56</t>
+          <t>-13,85; 51,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 57,48</t>
+          <t>-11,71; 54,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 46,5</t>
+          <t>-14,26; 47,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 3,7</t>
+          <t>-8,39; 5,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 10,2</t>
+          <t>-15,61; 10,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,14; -0,25</t>
+          <t>-23,29; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 5,36</t>
+          <t>-17,92; 4,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 12,56</t>
+          <t>-1,93; 13,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 22,33</t>
+          <t>-28,14; 23,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,56; -0,34</t>
+          <t>-40,4; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 14,01</t>
+          <t>-34,83; 13,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 15,67</t>
+          <t>-2,16; 16,4</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,15%</t>
+          <t>-1,7%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 15,26</t>
+          <t>-11,31; 14,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 28,72</t>
+          <t>-0,54; 27,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 12,68</t>
+          <t>-15,27; 13,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 10,31</t>
+          <t>-12,64; 8,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 26,82</t>
+          <t>-16,22; 25,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 70,52</t>
+          <t>-1,37; 61,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,85; 34,1</t>
+          <t>-29,08; 37,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 12,98</t>
+          <t>-14,08; 11,08</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,42</t>
+          <t>-5,17; 4,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,62</t>
+          <t>-4,1; 6,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,8</t>
+          <t>-5,51; 4,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 2,66</t>
+          <t>-3,02; 3,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 13,24</t>
+          <t>-13,33; 14,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 18,08</t>
+          <t>-10,93; 19,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 12,33</t>
+          <t>-14,99; 13,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,13</t>
+          <t>-3,45; 4,33</t>
         </is>
       </c>
     </row>
